--- a/Word.xlsx
+++ b/Word.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sangh\Desktop\Code\English_word\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F105088-9B25-4773-930F-32A7DAA64C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC72B93-D6DE-40C9-A7D8-A826C15CC07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{374DAD88-A01C-4036-B6AF-1C34CD303DA2}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2678" uniqueCount="2207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2683" uniqueCount="2211">
   <si>
     <t>뜻</t>
   </si>
@@ -21185,6 +21185,22 @@
   </si>
   <si>
     <t>The king sat upon his golden throne.</t>
+  </si>
+  <si>
+    <t>crisis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>violation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위반, 위배</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -40723,11 +40739,17 @@
       <c r="A671" s="28">
         <v>670</v>
       </c>
-      <c r="B671" s="28"/>
-      <c r="C671" s="28"/>
+      <c r="B671" s="28" t="s">
+        <v>2207</v>
+      </c>
+      <c r="C671" s="28" t="s">
+        <v>2208</v>
+      </c>
       <c r="D671" s="29"/>
       <c r="E671" s="28"/>
-      <c r="F671" s="30"/>
+      <c r="F671" s="30">
+        <v>46123</v>
+      </c>
       <c r="G671" s="28" t="str">
         <f>IF('단어 시험장'!E671="❌","❌","")</f>
         <v/>
@@ -40736,14 +40758,20 @@
         <f t="array" ref="H671">IF(B671="","",IF(COUNTIF($B$2:$B$501,B671)&gt;1,"No."&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(($B$2:$B$501=B671)*(ROW($B$2:$B$501)&lt;&gt;ROW(B671)),""&amp;$A$2:$A$501,"")),""))</f>
         <v/>
       </c>
-      <c r="I671" s="28"/>
+      <c r="I671" s="28" t="s">
+        <v>1433</v>
+      </c>
     </row>
     <row r="672" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A672" s="28">
         <v>671</v>
       </c>
-      <c r="B672" s="28"/>
-      <c r="C672" s="28"/>
+      <c r="B672" s="28" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C672" s="28" t="s">
+        <v>2210</v>
+      </c>
       <c r="D672" s="29"/>
       <c r="E672" s="28"/>
       <c r="F672" s="30"/>
